--- a/Maharashtra_5_Dams_Data.xlsx
+++ b/Maharashtra_5_Dams_Data.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -468,7 +468,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -553,7 +553,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -672,7 +672,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -742,7 +742,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>08/09/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05/09/2026</t>
+          <t>06/09/2026</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
